--- a/docs/clients/ss-marketing-master.xlsx
+++ b/docs/clients/ss-marketing-master.xlsx
@@ -7,21 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Юнит-экономика" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Маркетинг-план" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 План продаж ОП" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Набор 20-40-60" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Один клиент" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 План-график рекламы" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Креативы" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Бюджет 3 сценария" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 Тесты креативов" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Расходы" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Каналы продаж" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 ТЗ на правки" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 Нужные данные" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Источники" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0 Цели" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Юнит-экономика" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Маркетинг-план" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 План продаж ОП" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Набор 20-40-60" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Один клиент" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 План-график рекламы" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Креативы" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Бюджет 3 сценария" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 Тесты креативов" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Расходы" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Каналы продаж" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 ТЗ на правки" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 Нужные данные" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Источники" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -180,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -262,6 +263,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -709,8 +716,2467 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Цели набора (вводная владельца 17.08) и путь к 20 «Практикам»</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Цели ставит владелец — они выше прогноза, и это нормально: цель тянет, прогноз проверяет. Здесь — обратный расчёт: что должно стать правдой, чтобы цель была взята.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Формулировка</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Минимум</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Максимум</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕЛЬ: продажи тарифа «Практик» до 04.11</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Главная цель. Практик 1 659 € ранний / 1 869 € обычный.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>План на КАЖДЫЙ из тарифов</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Вводная владельца: мин/макс одинаковый на каждый тариф — это внутренние стретч-цели команды, не прогноз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Коммуникация НАРУЖУ (сайт, реклама, команда МИГ)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>20 участий</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>желательно 60</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Общая цель по всем тарифам вместе. Внутренние потарифные цели наружу не транслируем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Обратный расчёт: что нужно для 20 «Практиков» к 04.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Шаг воронки</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Норматив (совет)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Оплат «Практик»</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Цель</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Доля «Практика» в оплатах при Практик-центричных продажах</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ: интервью и лендинг продают ИМЕННО Практик (якорь), остальные тарифы — запасные позиции. Историческая доля — запрошена у Вали (лист 13, №3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Оплат всего (20 ÷ 0,65)</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>B11/B12</f>
+        <v/>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Формула ≈ 31 оплата — это ОПТИМИСТИЧНЫЙ сценарий таблицы (28) с небольшим превышением</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Интервью (÷ 0,60)</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>B13/0.6</f>
+        <v/>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>интервью→оплата 60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Заявок (÷ 0,55 доходимость)</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>B14/0.55</f>
+        <v/>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>с напоминаниями за 24ч/2ч</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Ответивших/дошедших (÷ 0,35)</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>B15/0.35</f>
+        <v/>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>ответ→заявка 35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Тёплых контактов (÷ 0,25)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>B16/0.25</f>
+        <v/>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>средний % ответа по пулам</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Наши пулы сегодня (лист 3)</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>'3 План продаж ОП'!B11</f>
+        <v/>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>≈ 841 контакт против ~1 066 нужных → дефицит ~21%. Чем закрываем: промо вебинаров в Meta (регистрации ×1,5), полная выгрузка email-базы, «назови коллегу» у выпускников</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Что меняем в плане ради цели (Практик-центричность)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>1. Интервью продаёт ТОЛЬКО Практик. Слушатель/Участник не предлагаем первыми — они существуют как «запасной выход» для тех, кто сам отказался. Якорение: разговор начинается с Практика и его супервизий.</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2. Лендинг: Практик визуально выделен как выбор программы (без слова «популярный» — по правилам сайта: иерархией и полнотой описания).</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>3. Дедлайны считаем по Практику: «ранний Практик 1 659 € до 30.09 — выгода 210 €» — во всех письмах дедлайна.</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>4. Апгрейд-механика: правило «повышение тарифа до 4-й встречи» — отдельная волна продаж ПОСЛЕ старта 04.12 (Слушатели и Участники получают предложение апгрейда на 1-3 неделях программы). Продажи Практика не заканчиваются 04.11!</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>5. Выпускники: их статус (цена Участника, доступ Практика) уже продаёт ценность Практика — в письме прямо называем это «доступ уровня Практик».</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>6. Вебинары: в конце каждого — разбор именно механики супервизий и конференции случаев (ядро Практика), а не общий анонс.</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>7. Бюджет под цель: 20 Практиков ≈ 31 оплата = оптимистичный сценарий → нужен оптимистичный бюджет 4 000 € и ВСЕ условия листа 4 (обзвонщик, вторая ступень цены, добор до 04.12).</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>ЧЕСТНАЯ РАМКА (правило «только правда»)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr"/>
+      <c r="C29" s="23" t="inlineStr"/>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>Цель 20 Практиков ≈ 31 оплата всего — на 55% выше реалистичного прогноза (20) и выше любого исторического потока (21 макс). Взять её можно только при одновременном выполнении ВСЕХ условий выше. Цель «60 Практиков» (≈92 оплаты) в это окно арифметически недостижима (пулы меньше в 3 раза) — это цель горизонта 2027, см. лист 4. Недельный контроль по Практику: 30.09 — 7, 25.10 — 13, 04.11 — 20.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="D29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Рекламный бюджет: сводная по трём сценариям</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Распределение — по вердикту совета: максимум в тёплые механики, посевы как тест, холод отдельной строкой на следующий поток.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Канал</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Пессимистично</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Реалистично</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Оптимистично</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Почему столько (источник)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Ретаргетинг Meta (пиксель + база + участники событий)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Совет: тёплое — приоритет №1 платных денег. CPL ~12 €, короткое плечо до оплаты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Промо вебинаров и ДОД (регистрации)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Вебинар — конвертер ×7 (факт 2025). Цена регистрации 3–6 €.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Посевы Telegram (2–3 канала, потом ещё 3–4)</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Совет: урезано с 800 — канал без факта конверсии для ЭТОГО продукта. Тест по протоколу R06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Meta холодный — вклад в СЛЕДУЮЩИЙ поток</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Лид холода в среднем не успевает пройти цикл до 04.11. Отдельная ROI-строка, не смешивать с целью «20 оплат».</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Яндекс Директ брендовый</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Совет: низкочастотка, цель — доля показов по бренду (защита от МИГиП/МГИ), а не CPL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Тесты креативов (внутри Meta, выделено)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>650</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>700</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Расчёт на листе 9 (~656 €). Совет: 300–500 € на 8–12 вариантов не хватало — сокращён до 6 вариантов. Пессимист: 4 варианта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Автовебинар: трафик на бот</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>С октября, работает на хвост и следующий поток.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Сервисы (TG-бот, email-платформа)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Стартуем на бесплатных тарифах; оптимист — платный тариф при росте базы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Резерв → в лидера по фактическому CAC</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Размораживается после замера 30.09. Триггеры: CAC канала ≤ плана ×1,3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B14" s="28">
+        <f>SUM(B5:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="28">
+        <f>SUM(C5:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="28">
+        <f>SUM(D5:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Должно сходиться с бюджетом сценария на листе 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Stop-loss (переносится из бюджет-модели, работает для любого сценария)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>• Канал не тратит больше 150 € без лида и больше 400 € без заявки «хочу на программу» — стоп и разбор.</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>• Meta: отключение объявления при CPL &gt; 40 € (при ≥500 показов). Посевы: после 2 первых каналов сверка цены перехода.</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>• Резерв не тратится до замера 30.09 — потом в канал-лидер по фактическому CAC (не по CPL!).</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>• Еженедельная сверка факта с этой таблицей; деньги перекладываются по фактическому CAC.</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A19:E19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Расчёт теста креативов (двухэтапный дизайн)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Методология: этап 1 — CTR-скрининг (дёшево отсеять слабые), этап 2 — CPL-раунд только на победителях. Так малый бюджет даёт статистически осмысленный выбор.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Этап 1. CTR-скрининг</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Обоснование</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Вариантов креативов</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Вердикт совета: 8–12 вариантов бюджет не тянет — 6 достаточно (3 крючка × 2 визуала).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Показов на вариант</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Расчёт мощности теста пропорций (наша методичка, раздел 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>CPM (узкая психо-аудитория, RU-speaking вне РФ)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ, калибруется в W04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Бюджет этапа 1</t>
+        </is>
+      </c>
+      <c r="B9" s="20">
+        <f>B6*B7/1000*B8</f>
+        <v/>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Формула: варианты × показы ÷ 1000 × CPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Этап 2. CPL-раунд (только победители)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Обоснование</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Победителей в раунде</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Топ-2 по CTR при не худшем CPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Лидов на вариант для решения</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Управленческий порог, не статистика (см. примечание)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Плановый CPL раунда</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Тёплые+ретаргет аудитории → ниже холодного CPL 20 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Бюджет этапа 2</t>
+        </is>
+      </c>
+      <c r="B16" s="20">
+        <f>B13*B14*B15</f>
+        <v/>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Формула: победители × лиды × CPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>ИТОГО бюджет теста</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>B9+B16</f>
+        <v/>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Заложено в строку «Тесты креативов» листа 8 (реалистично 550 €)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Правила теста</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>• Одна переменная за раз: сначала крючок (3 варианта при одном визуале), потом визуал.</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>• Решение по этапу 1 — CTR и CPC; решение по этапу 2 — CPL; масштабирование — по CAC (цена ОПЛАТЫ, не лида!).</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>• Аудитории этапов не пересекаются с боевым ретаргетом (исключения аудиторий), чтобы тест не крал дешёвые конверсии.</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>• Антифрод: только плейсменты лент (без Audience Network), лендинг вместо лид-форм, гео/язык проверяются в разбивке.</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Все расходы: предполагаемые, случайные, непредвиденные</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Чек-лист совета аудиторов: что обычно забывают в таких планах. Рекламный бюджет — лист 8; здесь всё ОСТАЛЬНОЕ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий / статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Комиссии рассрочек (Долями / Тинькофф)</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>3–8% от оплат в ₽</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>СТАВКА НЕИЗВЕСТНА — запрошена (типичный диапазон для продавца). Вычитать из выручки сразу, а не «потом».</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Комиссии международных платежей (EUR, конвертация)</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>1–4% + фикс</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Спред конвертации и SWIFT для оплат «картой любой страны». Уточнить у бухгалтерии клиента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Возвраты и отказы после оплаты</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>5–15% от оплат</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Типично для онлайн-образования (вердикт совета). Закладывать в пессимистичный кэшфлоу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Дизайнер креативов</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>нужна цифра</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Нанят, стоимость работ не сообщена — запрошена. Объём: ТЗ v2 (10 макетов) + афиши вебинаров + шаблон.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Вычитка журналистом</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>внутренняя</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Процесс агентства (агент-редактор), денежных затрат нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Сайт «Сложного случая»</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>0 €</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Статика по ТЗ, делает агентство/разработчик клиента. Если Tilda — от ~15 €/мес (проверить).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Вебинарная платформа</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>0–50 €/мес</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Zoom у клиента есть; хватит ли тарифа на 100+ участников — проверить ДО вебинара №1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TG-бот (регистрации, автовебинар)</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>0–20 €/мес</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Конструкторы ботов: бесплатный тариф на старте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Модерация и простой кампаний</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>риск времени</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Категория «образование/здоровье» у Meta проверяется строже: закладывать 1–2 дня на модерацию каждого запуска.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Бухгалтерия трёх юрлиц, валютный контроль</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>зона клиента</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>ООО Черногория + ИП РФ + самозанятый: время и % конвертаций. Не наш бюджет, но влияет на скорость запусков.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>НЕПРЕДВИДЕННЫЕ (буфер)</t>
+        </is>
+      </c>
+      <c r="B15" s="30">
+        <f>15%</f>
+        <v/>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Стандарт проектного управления: 10–20% медиабюджета. При базовом бюджете 2 500 € буфер = 375 € СВЕРХ бюджета — согласовать с клиентом заранее, чтобы не останавливать кампанию посреди теста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>ГЛАВНАЯ ДЫРА ДАННЫХ</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr"/>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Себестоимость программы (гонорары 11 преподавателей, супервизоров, платформа обучения) неизвестна агентству. Без неё вся таблица считает ВЫРУЧКУ, а не прибыль. Запрошено у клиента.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Каналы продаж: почему они, как тестируем, что работает</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Канал</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Почему он</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Как тестируем</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Что уже знаем (работает / нет)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Переписка WhatsApp/Telegram (менеджеры)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Политика клиента: звонков нет. Лиды сами оставили контакт</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>A/B: 3 версии первого сообщения на партии 10–20 отвалившихся (даёт Валя), потом лучшая — на все пулы</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>НЕ РАБОТАЕТ: «всё ли верно?» без ценности (факт: 90% игнор). ЖДЁМ: скрипт 3 касаний (подарок→событие→цена).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Email-цепочки</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>База есть, про программу ещё не писали — непуганый ресурс</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Замер open/click по каждому письму; 3 письма дедлайна 30.09 — отдельный замер</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Неизвестно: размер базы и её отклик. Бенчмарк образования: open ~28% (GetResponse 2024) — ориентир, не обещание.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Интервью (Zoom, ведущие)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Исторический конвертер 55–73% в оплату. Продаёт внимание, не скидка</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Фиксируем в Alfa: доходимость, длительность, исход. Напоминания за 24ч/2ч — тест влияния на доходимость</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>РАБОТАЕТ (факт). Узкое место — пропускная способность ведущих: проверить, сколько слотов в неделю реально.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Вебинары → заявка</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Механика 2025: конверсия 7,2% против 1% без прогрева</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Каждый вебинар: регистрации → живьём → заявки → оплаты. Сравниваем темы</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>РАБОТАЕТ (факт 2025). НЕ работает: узкие авторские темы летом (Орлова 18.07 — 2 регистрации, факт).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Обзвон (когда будет человек)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Speed-to-lead: голос конвертит выше переписки</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Первые 50 звонков по 95 лидам против переписки — сравнение конверсии в диалог</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Неизвестно. Блокер: человека нет (запрошен у клиента, п. 11 «Что нужно от МИГа»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Рассрочка/помодульная оплата</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Снимает разовый платёж. НО: барьер клиентов — график, не деньги (факт от Вали)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Тихая опция в оплате, НЕ строим кампанию вокруг неё. Замер: % выбравших рассрочку</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Помодульная РАБОТАЕТ (есть факт использования). Долями/Тинькофф — только карты РФ: международная часть не покрыта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Сарафан / рекомендации выпускников</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Факт 2025: 50% студентов не с рекламы</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>«Назови 1 коллегу» в письме выпускникам; замер: сколько имён пришло</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>РАБОТАЕТ пассивно. НЕ работало: промо «приведи и получи скидку» — ни одного использования (факт). Работает статус, не скидка.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ТЗ на правки (по итогам этого расчёта и совета)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Конкретные правки к сайту, процессу продаж и рекламной инфраструктуре. Дополняет «Открытые пункты» сайта и «Что нужно от МИГа».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Правка</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Кому</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Срок</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Зачем</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Сайт: добавить вторую ступень цены 01.11 (между ранней 30.09 и стартом)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>учредитель → сайт</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>19.08 (созвон)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>После 30.09 — 5 недель набора без единого дедлайна. Дедлайн — главный ускоритель цикла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Сайт: блок «Как программа ложится в ваш год» — расписание модулей, часы в неделю, совместимость с практикой</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>методолог + сайт</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>до 06.09</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Главная причина отказов — график и даты (факт от Вали). Отвечаем на неё ДО интервью.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Сайт: честно решить противоречие «3–4 часа в неделю» против реальной пятницы Практика (модуль 10:00–14:00 + психоанализ 17:00–19:00)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>методолог</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>до 06.09</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Открытый пункт №11 сайта. Обещание, которое не сойдётся с реальностью, убьёт сарафан.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Сайт/процесс: письменная политика зачёта часов МГИ (да/нет/частично)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>методолог</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>до 30.08</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Третья причина отказов. Менеджеры отвечают одинаково, слоты интервью не сгорают.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Лид-магнит: бесшовный доступ к «9 лекциям» (ссылка сразу после заявки, без личного кабинета)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>разработчик</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>до 06.09</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Сейчас логин/пароль теряют людей на входе (пункт 7 «Что нужно от МИГа»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Процесс: SLA первого касания ≤1 ч (горячие) / ≤4 ч (реанимация) — как KPI менеджеров в Alfa</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Валя</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>с W01</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Причина 90% игнора июля. Speed-to-lead ×21 (benchmarks.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Процесс: квал-вопрос про даты/график до записи на интервью + расписание в первом касании</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Валя</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>с W01</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Отсев главной причины отказа на входе воронки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Процесс: waitlist для «не подходит по датам» и решение о доборе до 04.12 — заранее, не 03.11</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>учредитель</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>19.08 (созвон)</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Пессимистичный сценарий (12 оплат) не дотягивает до минимума 20 — добор становится планом Б.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Реклама: UTM-разметка всех ссылок + поля источника в Alfa</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Тина</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>до 22.08</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Без атрибуции невозможно проверить план по каналам (вердикт совета).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Реклама: антифрод-настройки Meta (без Audience Network, лендинг вместо лид-форм, гео/язык в разбивке)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Тина</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>до запуска W04</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Июльский «фрод» — вероятно, настройки. Карантин-бюджет первой недели: 50 €/день максимум.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Онбординг оплативших: один личный кабинет, welcome-цепочка, честно про 2 супервизии</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>администрация</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>до 04.12</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Прошлый поток начался с волны негатива — это бьёт по сарафану следующего набора (пункт 12 клиента).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Таблица клиента (план 17.08): заменить допущения воронки на консервативные нормативы совета (ответ 15–30%, доходимость 55–60%, интервью→оплата 60–65%)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Тина</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>сделано в этом файле</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Исходные 45%/72%/73% превышали исторический максимум — план не может стоять на рекорде.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Какие данные нужны для точности (запрос клиенту)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Пока этих данных нет, помеченные ДОПУЩЕНИЕМ числа — оценки. Каждый ответ делает таблицу точнее: заменяешь голубую ячейку — всё пересчитывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Данные</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>У кого</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Что уточнит в таблице</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Себестоимость программы: гонорары преподавателей/супервизоров, платформа</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>учредитель</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Превратит расчёт выручки в расчёт ПРИБЫЛИ. Сейчас — главная дыра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Выгрузка Alfa: размеры пулов (отвалившиеся, email-база, база «9 лекций») с контактами</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Валя, до 20.08</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Лист 3: заменит допущения 50 и 300 фактами. От этого зависит, достижимы ли 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Разбивка прошлых потоков по тарифам (сколько брали Практик/Слушатель...)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Валя</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Состав оплат в сценариях (лист 1) — сейчас это план, не факт. Совет: 9 Практиков — оптимизм.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>История циклов сделки: какая доля сделок закрывалась быстрее 79 дней</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Валя (Alfa)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Главный вопрос плана: успевают ли лиды сентября оплатить до 04.11. Сейчас — экспертная оценка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Комиссии Долями/Тинькофф и международного эквайринга</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>бухгалтерия</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Лист 10: реальные ставки вместо диапазонов 3–8%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Стоимость дизайнера (ТЗ v2 + афиши + шаблон)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Тина</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Лист 10: последняя неизвестная строка расходов агентства.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Доступ к Meta-кабинету + выгрузка июльской кампании</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>учредитель, до 22.08</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Аудит «фрода»: настройки или канал. От этого — конфигурация всего платного Meta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Решение: добор до 04.12 разрешён?</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>учредитель, 19.08</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>План Б пессимистичного сценария. Без решения заранее W13–16 пропадают.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Вторая ступень цены 01.11: да/нет</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>учредитель, 19.08</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Дедлайн-механика октября (лист 6, W11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Человек на обзвон: будет/нет, когда</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>учредитель, до 30.08</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Каналы продаж: обзвон 95 лидов и отвалившихся. Без него — только переписка (конверсия ниже).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Имя/ИНН ИП МИГа</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Валя/учредитель</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Запуск Яндекс Директ от ИП + маркировка посевов (ОРД/erid).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Пропускная способность интервью: сколько слотов в неделю у ведущих</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>методолог</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Узкое горло воронки в октябре (лист 3): 33 интервью должны физически поместиться в календарь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Записи прошлых вебинаров + право использования</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>администрация</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Автовебинар (W08+): лучшая запись становится машиной следующего потока.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Источники данных и исследований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Правило агентства: у каждой цифры — источник и год. [A] — первичные данные клиента, [B] — отраслевые исследования, [C] — наши оценки, помеченные как допущения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Что даёт</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Класс / год</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Данные МИГ: xlsx «продвижение 2025–2026» (получен 07.08)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>CAC 72,3 €, CPL 4,87 €, конверсии 7,2%/1%, цикл сделки, 138 лидов 2025, квал-лид 25–44 €</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>[A] 2025–2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Реестр участников ППК 2023–2025 (получен 17.08)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Потоки 15/21/20, состав аудитории (89–100% женщины)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>[A] 2023–2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>План набора «Сложный случай» (файл клиента, 17.08)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Рамка: даты, тарифы, пулы, вебинарные факты (сексология/телесность 100+, Орлова — 2), ответы Вали</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>[A] 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Файл «Сайт: структура и тексты» (17.08)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Тарифы ранние/обычные, условия, скидки ДОД/ЯСНО, техтребования</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>[A] 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Переписка с Валей 08.08 (скриншоты)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Кампания отключена (фрод), нет звонков, email-база не тронута, барьеры «график/даты/зачёт часов», интервью→оплата 55–73%</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>[A] 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Касдев «Цифра» n=170 (R13)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Боли аудитории: «где брать клиентов» 83%, возражения «вода, нечёткие результаты»</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>[A] 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>R04 Юнит-экономика МИГ (наше исследование)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>LTV-маржа ~4 100 €, допустимый CAC 650–1 350 €</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>[C] 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>R05/benchmarks.md: WordStream / LocaliQ Facebook Ads Benchmarks</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>CPL образования ~21 € медиана; CPC/CTR ориентиры. wordstream.com/blog/ws/2024/04/29/facebook-ads-benchmarks</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>[B] 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Meta Business Help: learning phase</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>~50 конверсий/неделю на ад-сет для выхода из обучения; статзначимость теста 50–100 конверсий. facebook.com/business/help/112167992830700</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>[B] тек.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Lead response research (LeadResponseManagement.org; HBR «The Short Life of Online Sales Leads»)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Скорость первого касания: контакт в первые 5 минут кратно поднимает квалификацию (×21 против 30 мин); hbr.org/2011/03</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>[B] 2011/2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ON24 Webinar Benchmarks Report</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Доходимость вебинаров ~40% в среднем; с напоминаниями выше. on24.com/resources</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>[B] 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>GetResponse Email Marketing Benchmarks</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Open rate образования ~28% — ориентир для email-цепочек. getresponse.com/resources/reports</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>[B] 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>David Skok, forentrepreneurs.com</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Норма LTV/CAC ≥ 3 для устойчивой юнит-экономики. forentrepreneurs.com/startup-killer</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>[B] классика</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Deloitte / The CMO Survey</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Маркетинговый бюджет ~10% выручки компании в среднем. cmosurvey.org</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>[B] 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>422-ФЗ «О налоге на профессиональный доход»</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Ограничения самозанятых: агентские схемы запрещены, лимит 2,4 млн ₽/год</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>[B] 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>ad-forecasting-and-testing.md (наша методичка)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Двухэтапный дизайн тестов, расчёт мощности, правила очеловечивания текстов</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>[C] 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Протокол R06 (проверка Telegram-каналов)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TGStat-метрики канала до покупки посева</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>[C] 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Честная оговорка</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Класс [B] — ориентиры рынка, они НЕ заменяют наши факты: везде, где есть данные МИГ [A], план опирается на них. Все допущения [C] выделены голубым и пересчитываются заменой одной ячейки.</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B23:C23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1048,1775 +3514,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Расчёт теста креативов (двухэтапный дизайн)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Методология: этап 1 — CTR-скрининг (дёшево отсеять слабые), этап 2 — CPL-раунд только на победителях. Так малый бюджет даёт статистически осмысленный выбор.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Этап 1. CTR-скрининг</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Параметр</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Обоснование</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Вариантов креативов</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Вердикт совета: 8–12 вариантов бюджет не тянет — 6 достаточно (3 крючка × 2 визуала).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Показов на вариант</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n">
-        <v>7700</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Расчёт мощности теста пропорций (наша методичка, раздел 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>CPM (узкая психо-аудитория, RU-speaking вне РФ)</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>ДОПУЩЕНИЕ, калибруется в W04</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Бюджет этапа 1</t>
-        </is>
-      </c>
-      <c r="B9" s="20">
-        <f>B6*B7/1000*B8</f>
-        <v/>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Формула: варианты × показы ÷ 1000 × CPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Этап 2. CPL-раунд (только победители)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Параметр</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Обоснование</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Победителей в раунде</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Топ-2 по CTR при не худшем CPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Лидов на вариант для решения</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Управленческий порог, не статистика (см. примечание)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Плановый CPL раунда</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Тёплые+ретаргет аудитории → ниже холодного CPL 20 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Бюджет этапа 2</t>
-        </is>
-      </c>
-      <c r="B16" s="20">
-        <f>B13*B14*B15</f>
-        <v/>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Формула: победители × лиды × CPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>ИТОГО бюджет теста</t>
-        </is>
-      </c>
-      <c r="B17" s="28">
-        <f>B9+B16</f>
-        <v/>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>Заложено в строку «Тесты креативов» листа 8 (реалистично 550 €)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Правила теста</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>• Одна переменная за раз: сначала крючок (3 варианта при одном визуале), потом визуал.</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>• Решение по этапу 1 — CTR и CPC; решение по этапу 2 — CPL; масштабирование — по CAC (цена ОПЛАТЫ, не лида!).</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>• Аудитории этапов не пересекаются с боевым ретаргетом (исключения аудиторий), чтобы тест не крал дешёвые конверсии.</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>• Антифрод: только плейсменты лент (без Audience Network), лендинг вместо лид-форм, гео/язык проверяются в разбивке.</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Все расходы: предполагаемые, случайные, непредвиденные</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Чек-лист совета аудиторов: что обычно забывают в таких планах. Рекламный бюджет — лист 8; здесь всё ОСТАЛЬНОЕ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Оценка</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Комментарий / статус</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Комиссии рассрочек (Долями / Тинькофф)</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>3–8% от оплат в ₽</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>СТАВКА НЕИЗВЕСТНА — запрошена (типичный диапазон для продавца). Вычитать из выручки сразу, а не «потом».</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Комиссии международных платежей (EUR, конвертация)</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>1–4% + фикс</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Спред конвертации и SWIFT для оплат «картой любой страны». Уточнить у бухгалтерии клиента.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Возвраты и отказы после оплаты</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>5–15% от оплат</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Типично для онлайн-образования (вердикт совета). Закладывать в пессимистичный кэшфлоу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Дизайнер креативов</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>нужна цифра</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Нанят, стоимость работ не сообщена — запрошена. Объём: ТЗ v2 (10 макетов) + афиши вебинаров + шаблон.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Вычитка журналистом</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>внутренняя</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Процесс агентства (агент-редактор), денежных затрат нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Сайт «Сложного случая»</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>0 €</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Статика по ТЗ, делает агентство/разработчик клиента. Если Tilda — от ~15 €/мес (проверить).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Вебинарная платформа</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>0–50 €/мес</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Zoom у клиента есть; хватит ли тарифа на 100+ участников — проверить ДО вебинара №1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TG-бот (регистрации, автовебинар)</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>0–20 €/мес</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Конструкторы ботов: бесплатный тариф на старте.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Модерация и простой кампаний</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="inlineStr">
-        <is>
-          <t>риск времени</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Категория «образование/здоровье» у Meta проверяется строже: закладывать 1–2 дня на модерацию каждого запуска.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Бухгалтерия трёх юрлиц, валютный контроль</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>зона клиента</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>ООО Черногория + ИП РФ + самозанятый: время и % конвертаций. Не наш бюджет, но влияет на скорость запусков.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>НЕПРЕДВИДЕННЫЕ (буфер)</t>
-        </is>
-      </c>
-      <c r="B15" s="30">
-        <f>15%</f>
-        <v/>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Стандарт проектного управления: 10–20% медиабюджета. При базовом бюджете 2 500 € буфер = 375 € СВЕРХ бюджета — согласовать с клиентом заранее, чтобы не останавливать кампанию посреди теста.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>ГЛАВНАЯ ДЫРА ДАННЫХ</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr"/>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>Себестоимость программы (гонорары 11 преподавателей, супервизоров, платформа обучения) неизвестна агентству. Без неё вся таблица считает ВЫРУЧКУ, а не прибыль. Запрошено у клиента.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Каналы продаж: почему они, как тестируем, что работает</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Канал</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Почему он</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Как тестируем</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Что уже знаем (работает / нет)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Переписка WhatsApp/Telegram (менеджеры)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Политика клиента: звонков нет. Лиды сами оставили контакт</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>A/B: 3 версии первого сообщения на партии 10–20 отвалившихся (даёт Валя), потом лучшая — на все пулы</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>НЕ РАБОТАЕТ: «всё ли верно?» без ценности (факт: 90% игнор). ЖДЁМ: скрипт 3 касаний (подарок→событие→цена).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Email-цепочки</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>База есть, про программу ещё не писали — непуганый ресурс</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Замер open/click по каждому письму; 3 письма дедлайна 30.09 — отдельный замер</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Неизвестно: размер базы и её отклик. Бенчмарк образования: open ~28% (GetResponse 2024) — ориентир, не обещание.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Интервью (Zoom, ведущие)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Исторический конвертер 55–73% в оплату. Продаёт внимание, не скидка</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Фиксируем в Alfa: доходимость, длительность, исход. Напоминания за 24ч/2ч — тест влияния на доходимость</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>РАБОТАЕТ (факт). Узкое место — пропускная способность ведущих: проверить, сколько слотов в неделю реально.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Вебинары → заявка</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Механика 2025: конверсия 7,2% против 1% без прогрева</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Каждый вебинар: регистрации → живьём → заявки → оплаты. Сравниваем темы</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>РАБОТАЕТ (факт 2025). НЕ работает: узкие авторские темы летом (Орлова 18.07 — 2 регистрации, факт).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Обзвон (когда будет человек)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Speed-to-lead: голос конвертит выше переписки</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Первые 50 звонков по 95 лидам против переписки — сравнение конверсии в диалог</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Неизвестно. Блокер: человека нет (запрошен у клиента, п. 11 «Что нужно от МИГа»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Рассрочка/помодульная оплата</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Снимает разовый платёж. НО: барьер клиентов — график, не деньги (факт от Вали)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Тихая опция в оплате, НЕ строим кампанию вокруг неё. Замер: % выбравших рассрочку</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Помодульная РАБОТАЕТ (есть факт использования). Долями/Тинькофф — только карты РФ: международная часть не покрыта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Сарафан / рекомендации выпускников</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Факт 2025: 50% студентов не с рекламы</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>«Назови 1 коллегу» в письме выпускникам; замер: сколько имён пришло</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>РАБОТАЕТ пассивно. НЕ работало: промо «приведи и получи скидку» — ни одного использования (факт). Работает статус, не скидка.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ТЗ на правки (по итогам этого расчёта и совета)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Конкретные правки к сайту, процессу продаж и рекламной инфраструктуре. Дополняет «Открытые пункты» сайта и «Что нужно от МИГа».</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Правка</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Кому</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Срок</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Зачем</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Сайт: добавить вторую ступень цены 01.11 (между ранней 30.09 и стартом)</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>учредитель → сайт</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>19.08 (созвон)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>После 30.09 — 5 недель набора без единого дедлайна. Дедлайн — главный ускоритель цикла.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Сайт: блок «Как программа ложится в ваш год» — расписание модулей, часы в неделю, совместимость с практикой</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>методолог + сайт</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>до 06.09</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Главная причина отказов — график и даты (факт от Вали). Отвечаем на неё ДО интервью.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Сайт: честно решить противоречие «3–4 часа в неделю» против реальной пятницы Практика (модуль 10:00–14:00 + психоанализ 17:00–19:00)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>методолог</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>до 06.09</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Открытый пункт №11 сайта. Обещание, которое не сойдётся с реальностью, убьёт сарафан.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Сайт/процесс: письменная политика зачёта часов МГИ (да/нет/частично)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>методолог</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>до 30.08</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Третья причина отказов. Менеджеры отвечают одинаково, слоты интервью не сгорают.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Лид-магнит: бесшовный доступ к «9 лекциям» (ссылка сразу после заявки, без личного кабинета)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>разработчик</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>до 06.09</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Сейчас логин/пароль теряют людей на входе (пункт 7 «Что нужно от МИГа»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Процесс: SLA первого касания ≤1 ч (горячие) / ≤4 ч (реанимация) — как KPI менеджеров в Alfa</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Валя</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>с W01</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Причина 90% игнора июля. Speed-to-lead ×21 (benchmarks.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Процесс: квал-вопрос про даты/график до записи на интервью + расписание в первом касании</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Валя</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>с W01</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Отсев главной причины отказа на входе воронки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Процесс: waitlist для «не подходит по датам» и решение о доборе до 04.12 — заранее, не 03.11</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>учредитель</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>19.08 (созвон)</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Пессимистичный сценарий (12 оплат) не дотягивает до минимума 20 — добор становится планом Б.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Реклама: UTM-разметка всех ссылок + поля источника в Alfa</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Тина</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>до 22.08</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Без атрибуции невозможно проверить план по каналам (вердикт совета).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Реклама: антифрод-настройки Meta (без Audience Network, лендинг вместо лид-форм, гео/язык в разбивке)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Тина</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>до запуска W04</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Июльский «фрод» — вероятно, настройки. Карантин-бюджет первой недели: 50 €/день максимум.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Онбординг оплативших: один личный кабинет, welcome-цепочка, честно про 2 супервизии</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>администрация</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>до 04.12</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Прошлый поток начался с волны негатива — это бьёт по сарафану следующего набора (пункт 12 клиента).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Таблица клиента (план 17.08): заменить допущения воронки на консервативные нормативы совета (ответ 15–30%, доходимость 55–60%, интервью→оплата 60–65%)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Тина</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>сделано в этом файле</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Исходные 45%/72%/73% превышали исторический максимум — план не может стоять на рекорде.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Какие данные нужны для точности (запрос клиенту)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Пока этих данных нет, помеченные ДОПУЩЕНИЕМ числа — оценки. Каждый ответ делает таблицу точнее: заменяешь голубую ячейку — всё пересчитывается.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Данные</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>У кого</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Что уточнит в таблице</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Себестоимость программы: гонорары преподавателей/супервизоров, платформа</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>учредитель</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Превратит расчёт выручки в расчёт ПРИБЫЛИ. Сейчас — главная дыра.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Выгрузка Alfa: размеры пулов (отвалившиеся, email-база, база «9 лекций») с контактами</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Валя, до 20.08</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Лист 3: заменит допущения 50 и 300 фактами. От этого зависит, достижимы ли 20.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Разбивка прошлых потоков по тарифам (сколько брали Практик/Слушатель...)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Валя</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Состав оплат в сценариях (лист 1) — сейчас это план, не факт. Совет: 9 Практиков — оптимизм.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>История циклов сделки: какая доля сделок закрывалась быстрее 79 дней</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Валя (Alfa)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Главный вопрос плана: успевают ли лиды сентября оплатить до 04.11. Сейчас — экспертная оценка.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Комиссии Долями/Тинькофф и международного эквайринга</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>бухгалтерия</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Лист 10: реальные ставки вместо диапазонов 3–8%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Стоимость дизайнера (ТЗ v2 + афиши + шаблон)</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Тина</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Лист 10: последняя неизвестная строка расходов агентства.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Доступ к Meta-кабинету + выгрузка июльской кампании</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>учредитель, до 22.08</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Аудит «фрода»: настройки или канал. От этого — конфигурация всего платного Meta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Решение: добор до 04.12 разрешён?</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>учредитель, 19.08</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>План Б пессимистичного сценария. Без решения заранее W13–16 пропадают.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Вторая ступень цены 01.11: да/нет</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>учредитель, 19.08</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Дедлайн-механика октября (лист 6, W11).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Человек на обзвон: будет/нет, когда</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>учредитель, до 30.08</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Каналы продаж: обзвон 95 лидов и отвалившихся. Без него — только переписка (конверсия ниже).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Имя/ИНН ИП МИГа</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Валя/учредитель</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Запуск Яндекс Директ от ИП + маркировка посевов (ОРД/erid).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Пропускная способность интервью: сколько слотов в неделю у ведущих</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>методолог</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Узкое горло воронки в октябре (лист 3): 33 интервью должны физически поместиться в календарь.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Записи прошлых вебинаров + право использования</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>администрация</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Автовебинар (W08+): лучшая запись становится машиной следующего потока.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Источники данных и исследований</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Правило агентства: у каждой цифры — источник и год. [A] — первичные данные клиента, [B] — отраслевые исследования, [C] — наши оценки, помеченные как допущения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Что даёт</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Класс / год</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Данные МИГ: xlsx «продвижение 2025–2026» (получен 07.08)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CAC 72,3 €, CPL 4,87 €, конверсии 7,2%/1%, цикл сделки, 138 лидов 2025, квал-лид 25–44 €</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>[A] 2025–2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Реестр участников ППК 2023–2025 (получен 17.08)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Потоки 15/21/20, состав аудитории (89–100% женщины)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>[A] 2023–2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>План набора «Сложный случай» (файл клиента, 17.08)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Рамка: даты, тарифы, пулы, вебинарные факты (сексология/телесность 100+, Орлова — 2), ответы Вали</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>[A] 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Файл «Сайт: структура и тексты» (17.08)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Тарифы ранние/обычные, условия, скидки ДОД/ЯСНО, техтребования</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>[A] 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Переписка с Валей 08.08 (скриншоты)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Кампания отключена (фрод), нет звонков, email-база не тронута, барьеры «график/даты/зачёт часов», интервью→оплата 55–73%</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>[A] 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Касдев «Цифра» n=170 (R13)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Боли аудитории: «где брать клиентов» 83%, возражения «вода, нечёткие результаты»</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>[A] 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>R04 Юнит-экономика МИГ (наше исследование)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>LTV-маржа ~4 100 €, допустимый CAC 650–1 350 €</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>[C] 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>R05/benchmarks.md: WordStream / LocaliQ Facebook Ads Benchmarks</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>CPL образования ~21 € медиана; CPC/CTR ориентиры. wordstream.com/blog/ws/2024/04/29/facebook-ads-benchmarks</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>[B] 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Meta Business Help: learning phase</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>~50 конверсий/неделю на ад-сет для выхода из обучения; статзначимость теста 50–100 конверсий. facebook.com/business/help/112167992830700</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>[B] тек.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Lead response research (LeadResponseManagement.org; HBR «The Short Life of Online Sales Leads»)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Скорость первого касания: контакт в первые 5 минут кратно поднимает квалификацию (×21 против 30 мин); hbr.org/2011/03</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>[B] 2011/2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>ON24 Webinar Benchmarks Report</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Доходимость вебинаров ~40% в среднем; с напоминаниями выше. on24.com/resources</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>[B] 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>GetResponse Email Marketing Benchmarks</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Open rate образования ~28% — ориентир для email-цепочек. getresponse.com/resources/reports</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>[B] 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>David Skok, forentrepreneurs.com</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Норма LTV/CAC ≥ 3 для устойчивой юнит-экономики. forentrepreneurs.com/startup-killer</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>[B] классика</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Deloitte / The CMO Survey</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Маркетинговый бюджет ~10% выручки компании в среднем. cmosurvey.org</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>[B] 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>422-ФЗ «О налоге на профессиональный доход»</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Ограничения самозанятых: агентские схемы запрещены, лимит 2,4 млн ₽/год</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>[B] 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>ad-forecasting-and-testing.md (наша методичка)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Двухэтапный дизайн тестов, расчёт мощности, правила очеловечивания текстов</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>[C] 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Протокол R06 (проверка Telegram-каналов)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>TGStat-метрики канала до покупки посева</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>[C] 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Честная оговорка</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Класс [B] — ориентиры рынка, они НЕ заменяют наши факты: везде, где есть данные МИГ [A], план опирается на них. Все допущения [C] выделены голубым и пересчитываются заменой одной ячейки.</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B23:C23"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3455,14 +4160,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
@@ -3706,14 +4411,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -4213,14 +4918,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -4404,14 +5109,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -4554,14 +5259,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -5055,14 +5760,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -5387,336 +6092,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Рекламный бюджет: сводная по трём сценариям</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Распределение — по вердикту совета: максимум в тёплые механики, посевы как тест, холод отдельной строкой на следующий поток.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Канал</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Пессимистично</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Реалистично</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Оптимистично</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Почему столько (источник)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Ретаргетинг Meta (пиксель + база + участники событий)</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Совет: тёплое — приоритет №1 платных денег. CPL ~12 €, короткое плечо до оплаты.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Промо вебинаров и ДОД (регистрации)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Вебинар — конвертер ×7 (факт 2025). Цена регистрации 3–6 €.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Посевы Telegram (2–3 канала, потом ещё 3–4)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>450</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Совет: урезано с 800 — канал без факта конверсии для ЭТОГО продукта. Тест по протоколу R06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Meta холодный — вклад в СЛЕДУЮЩИЙ поток</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>600</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Лид холода в среднем не успевает пройти цикл до 04.11. Отдельная ROI-строка, не смешивать с целью «20 оплат».</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Яндекс Директ брендовый</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Совет: низкочастотка, цель — доля показов по бренду (защита от МИГиП/МГИ), а не CPL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Тесты креативов (внутри Meta, выделено)</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>650</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Расчёт на листе 9 (~656 €). Совет: 300–500 € на 8–12 вариантов не хватало — сокращён до 6 вариантов. Пессимист: 4 варианта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Автовебинар: трафик на бот</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>С октября, работает на хвост и следующий поток.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Сервисы (TG-бот, email-платформа)</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Стартуем на бесплатных тарифах; оптимист — платный тариф при росте базы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Резерв → в лидера по фактическому CAC</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Размораживается после замера 30.09. Триггеры: CAC канала ≤ плана ×1,3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B14" s="28">
-        <f>SUM(B5:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="28">
-        <f>SUM(C5:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="28">
-        <f>SUM(D5:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>Должно сходиться с бюджетом сценария на листе 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Stop-loss (переносится из бюджет-модели, работает для любого сценария)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>• Канал не тратит больше 150 € без лида и больше 400 € без заявки «хочу на программу» — стоп и разбор.</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>• Meta: отключение объявления при CPL &gt; 40 € (при ≥500 показов). Посевы: после 2 первых каналов сверка цены перехода.</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>• Резерв не тратится до замера 30.09 — потом в канал-лидер по фактическому CAC (не по CPL!).</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>• Еженедельная сверка факта с этой таблицей; деньги перекладываются по фактическому CAC.</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A19:E19"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/clients/ss-marketing-master.xlsx
+++ b/docs/clients/ss-marketing-master.xlsx
@@ -181,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -271,6 +271,15 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -717,7 +726,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -3175,7 +3184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3498,14 +3507,22 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Почему у пессимиста бюджет МЕНЬШЕ: пессимистичный сценарий = плохой отклик, а при плохом отклике stop-loss останавливает траты (150 € без лида → стоп). Худший случай «потратили много — получили мало» посчитан отдельно: лист 1, раздел Г (стресс-тест).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B12:C12"/>
@@ -3520,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4150,8 +4167,126 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>Г. СТРЕСС-ТЕСТ: «потратили много — получили мало» (вопрос владельца 17.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Это НЕ сценарий плана, а проверка: что будет, если stop-loss не сработает и весь оптимистичный бюджет сгорит при пессимистичном отклике.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="inlineStr"/>
+      <c r="D42" s="34" t="inlineStr"/>
+      <c r="E42" s="34" t="inlineStr">
+        <is>
+          <t>Что это означает</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>Потрачено (весь оптимистичный бюджет)</t>
+        </is>
+      </c>
+      <c r="B43" s="36" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Ввод: худший случай трат</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>Оплат получено (пессимистичный отклик)</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Ввод: худший случай результата</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>Из них с рекламы</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Ввод: тёплые пулы дали остальное</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="38" t="inlineStr">
+        <is>
+          <t>CAC блендед в стресс-тесте</t>
+        </is>
+      </c>
+      <c r="B46" s="39">
+        <f>B43/B44</f>
+        <v/>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>333 € — больно, но выручка 16 200 € всё равно покрывает бюджет с запасом ×4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="38" t="inlineStr">
+        <is>
+          <t>CAC рекламного клиента в стресс-тесте</t>
+        </is>
+      </c>
+      <c r="B47" s="40">
+        <f>B43/B45</f>
+        <v/>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2 000 € — ВЫШЕ допустимого CAC 1 350 € (R04). Именно от этого защищают stop-loss и еженедельная сверка: деньги останавливаются ДО того, как дойдут до этой точки</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Защита от стресс-теста (почему он не должен случиться): 1) резерв 500-750 € заморожен до замера 30.09; 2) канал не тратит &gt;150 € без лида и &gt;400 € без заявки; 3) холодный Meta стартует только ПОСЛЕ аудита фрода; 4) еженедельная сверка CAC — деньги перекладываются каждые 7 дней, а не в конце.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B32:E32"/>
   </mergeCells>

--- a/docs/clients/ss-marketing-master.xlsx
+++ b/docs/clients/ss-marketing-master.xlsx
@@ -4387,12 +4387,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Реанимация 95 лидов (скрипт 3 касаний готов, партии 20–30/день); письмо 56 выпускникам: статус выпускника (повтор по цене «Участник» с доступом «Практик») + просьба назвать 1 коллегу; обзвон отвалившихся</t>
+          <t>Реактивация 53 поимённых контактов (41 отвал + 12 недошедших) — WhatsApp с личного номера, 3 касания («старт перенесён на 04.12 + рассрочка от 69 €/мес»); письмо 56 выпускникам: «что починили» → статус выпускника → «назови 1 коллегу». Игнор-лиды июля СНЯТЫ (Молдова/Болгария, 0 из РФ) — только тест 10 контактов</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Самые дешёвые оплаты. Факт 2025: 50% студентов — не с рекламы. Скорость касания ×21 к квалификации (звонок ≤5 мин против 30, benchmarks.md)</t>
+          <t>Самые дешёвые оплаты. Факт 2025: 50% студентов — не с рекламы. 34 из 41 отвала — март–май: им сейчас ровно цикл сделки, самое время вернуться</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4619,72 +4619,72 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>95 необработанных лидов июля</t>
+          <t>Реактивация: отвал (поимённо, факт 17.08)</t>
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Ответ 30%: свежие, сами оставляли заявку. Скрипт реанимации, партии 20–30/день. SLA ответа ≤4 ч.</t>
+          <t>ФАКТ: 34 из 41 — отвал марта–мая, им сейчас ровно цикл сделки. WhatsApp с личного номера, 3 касания: «изменились две вещи — старт 04.12 и рассрочка от 69 €/мес».</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>56 выпускников трёх потоков</t>
+          <t>Реактивация: недошедшие до старта</t>
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Личное письмо + статус выпускника + «назови 1 коллегу». Знают продукт — конверсия выше.</t>
+          <t>ФАКТ поимённо, 11 из 12 в WhatsApp. Дошли до списков групп и не стартовали — новости о переносе и рассрочке бьют в их причину отказа.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Отвалившиеся прошлых наборов</t>
+          <t>56 выпускников трёх потоков</t>
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="D8" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="18" t="n">
-        <v>2</v>
-      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>РАЗМЕР — ДОПУЩЕНИЕ, нужна выгрузка Alfa. Барьер — график: сразу показываем расписание.</t>
+          <t>Письмо №1 «что починили», №2 статус выпускника, №3 «назови коллегу». В контакт-листе 68: WhatsApp 47 / Telegram 20.</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>РАЗМЕР — ДОПУЩЕНИЕ, нужен факт. Цепочка 3 писем + починить бесшовный доступ к лекциям.</t>
+          <t>РАЗМЕР — ДОПУЩЕНИЕ, единственный неизвестный пул (запрос у Вали до 20.08). Цепочка на вебинары + починить бесшовный доступ.</t>
         </is>
       </c>
     </row>
@@ -4737,240 +4737,252 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Игнор-лиды июля — СНЯТЫ (было 3 оплаты в плане)</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>ФАКТ 17.08: Молдова 58% / Болгария 13%, НОЛЬ из России (Meta не показывает в РФ), 100% без ответа за 19 дней. Оставлен тест на 10 контактах, ожидание 0–1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>ИТОГО (реалистичный)</t>
         </is>
       </c>
-      <c r="B11" s="25">
-        <f>SUM(B6:B10)</f>
+      <c r="B12" s="25">
+        <f>SUM(B6:B11)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
-        <f>SUM(D6:D10)</f>
+      <c r="D12" s="25">
+        <f>SUM(D6:D11)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
-        <f>SUM(E6:E10)</f>
+      <c r="E12" s="25">
+        <f>SUM(E6:E11)</f>
         <v/>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>Оплаты сходятся с реалистичным сценарием юнит-экономики (20)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Б. Проверка нагрузки (вердикт совета: 20–30 касаний/день на менеджера)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Контактов во всех пулах</t>
-        </is>
-      </c>
-      <c r="B15" s="9">
-        <f>SUM(B6:B10)</f>
-        <v/>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Формула</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Касаний всего (×2,2 на контакт)</t>
+          <t>Контактов во всех пулах</t>
         </is>
       </c>
       <c r="B16" s="9">
-        <f>B15*2.2</f>
+        <f>SUM(B6:B11)</f>
         <v/>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Первое касание + напоминание + дожим</t>
+          <t>Формула</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>Касаний всего (×2,2 на контакт)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>B16*2.2</f>
+        <v/>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Первое касание + напоминание + дожим</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>Рабочих дней до 04.11</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B18" s="18" t="n">
         <v>56</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>79 календарных дней ≈ 56 рабочих</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Касаний в день на отдел</t>
         </is>
       </c>
-      <c r="B18" s="27">
-        <f>B16/B17</f>
+      <c r="B19" s="27">
+        <f>B17/B18</f>
         <v/>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Норматив совета: 20–30/день на менеджера = до 60 на двоих. Если выше — нужен обзвонщик (запрошен у клиента)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>В. Недельные цели по оплатам (кумулятивно)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Контрольная точка</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Пессимистично</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Реалистично</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Оптимистично</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Что делает контрольная точка</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>30.09 — закрытие ранней цены</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Первый большой дедлайн. Если факт &lt; половины цели — пересбор плана, совет с владельцем.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>25.10 — после вебинара №3</t>
+          <t>30.09 — закрытие ранней цены</t>
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Второй замер. Решение об интенсивности финального дожима.</t>
+          <t>Первый большой дедлайн. Если факт &lt; половины цели — пересбор плана, совет с владельцем.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>25.10 — после вебинара №3</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Второй замер. Решение об интенсивности финального дожима.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>04.11 — дедлайн набора</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B25" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C25" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D25" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Минимум клиента: 20. Пессимист НЕ дотягивает — тогда добор до 04.12 (нужно решение клиента заранее!).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Г. Правила работы (вердикт совета продаж)</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>• SLA первого касания: ≤1 часа для горячих (вебинары, ДОД, сайт), ≤4 часов для реанимации. Это KPI, а не пожелание.</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>• Квал-вопрос про даты и график ДО записи на интервью + расписание модулей в первом касании — главная причина отказов отсеивается на входе, слоты интервью не сгорают.</t>
+          <t>• SLA первого касания: ≤1 часа для горячих (вебинары, ДОД, сайт), ≤4 часов для реанимации. Это KPI, а не пожелание.</t>
         </is>
       </c>
       <c r="B28" s="17" t="n"/>
@@ -4982,7 +4994,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>• Политика зачёта часов МГИ — письменно (да/нет/частично). Запросить у методолога.</t>
+          <t>• Квал-вопрос про даты и график ДО записи на интервью + расписание модулей в первом касании — главная причина отказов отсеивается на входе, слоты интервью не сгорают.</t>
         </is>
       </c>
       <c r="B29" s="17" t="n"/>
@@ -4994,7 +5006,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>• Не подходит по датам → лист ожидания следующего потока (это будущая выручка, не отказ).</t>
+          <t>• Политика зачёта часов МГИ — письменно (да/нет/частично). Запросить у методолога.</t>
         </is>
       </c>
       <c r="B30" s="17" t="n"/>
@@ -5006,7 +5018,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>• Напоминания об интервью: за 24 ч и за 2 ч (голосовое/сообщение) — иначе доходимость падает с 70% к 50%.</t>
+          <t>• Не подходит по датам → лист ожидания следующего потока (это будущая выручка, не отказ).</t>
         </is>
       </c>
       <c r="B31" s="17" t="n"/>
@@ -5018,7 +5030,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>• После 3-го касания без ответа — пауза до следующего события (вебинар/дедлайн), не спамить.</t>
+          <t>• Напоминания об интервью: за 24 ч и за 2 ч (голосовое/сообщение) — иначе доходимость падает с 70% к 50%.</t>
         </is>
       </c>
       <c r="B32" s="17" t="n"/>
@@ -5030,7 +5042,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>• KPI менеджера: оплаты + соблюдение SLA + доходимость до интервью. Мотивация: повышенный % за «Практик», бонус-спиф за 20-ю оплату потока (взятие рекорда).</t>
+          <t>• После 3-го касания без ответа — пауза до следующего события (вебинар/дедлайн), не спамить.</t>
         </is>
       </c>
       <c r="B33" s="17" t="n"/>
@@ -5039,13 +5051,25 @@
       <c r="E33" s="17" t="n"/>
       <c r="F33" s="7" t="n"/>
     </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>• KPI менеджера: оплаты + соблюдение SLA + доходимость до интервью. Мотивация: повышенный % за «Практик», бонус-спиф за 20-ю оплату потока (взятие рекорда).</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>

--- a/docs/clients/ss-marketing-master.xlsx
+++ b/docs/clients/ss-marketing-master.xlsx
@@ -1208,7 +1208,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Meta холодный — вклад в СЛЕДУЮЩИЙ поток</t>
+          <t>Холод: VK от ИП МИГа + Meta — вклад в СЛЕДУЮЩИЙ поток</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Лид холода в среднем не успевает пройти цикл до 04.11. Отдельная ROI-строка, не смешивать с целью «20 оплат».</t>
+          <t>Кабинет VK от ИП открыт 17.08 — ₽-ядро РФ. Лид холода в среднем не успевает пройти цикл до 04.11. Отдельная ROI-строка, не смешивать с целью «20 оплат».</t>
         </is>
       </c>
     </row>
